--- a/Outputs/Recycling_Plot_Data/ACCII/01b_Geofacet_RegionMass_2050_data_ACCII.xlsx
+++ b/Outputs/Recycling_Plot_Data/ACCII/01b_Geofacet_RegionMass_2050_data_ACCII.xlsx
@@ -413,7 +413,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.7496032910202518</v>
+        <v>0.7488521272651167</v>
       </c>
     </row>
     <row r="4">
@@ -433,7 +433,7 @@
         </is>
       </c>
       <c r="D4">
-        <v>1.403681196479397</v>
+        <v>1.402274593211788</v>
       </c>
     </row>
     <row r="5">
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="D27">
-        <v>0.08671258408835963</v>
+        <v>0.08662569099295631</v>
       </c>
     </row>
     <row r="28">
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="D29">
-        <v>0.6659696282424172</v>
+        <v>0.6659083560325868</v>
       </c>
     </row>
     <row r="30">
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="D33">
-        <v>2.444511980532543</v>
+        <v>2.442062379762689</v>
       </c>
     </row>
     <row r="34">
@@ -1033,7 +1033,7 @@
         </is>
       </c>
       <c r="D34">
-        <v>1.527764389965578</v>
+        <v>1.526233445198025</v>
       </c>
     </row>
     <row r="35">
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="D39">
-        <v>3.398063015225808</v>
+        <v>3.39465787839506</v>
       </c>
     </row>
     <row r="40">
@@ -1153,7 +1153,7 @@
         </is>
       </c>
       <c r="D40">
-        <v>3.71606127278493</v>
+        <v>3.712337475713313</v>
       </c>
     </row>
     <row r="41">
@@ -1253,7 +1253,7 @@
         </is>
       </c>
       <c r="D45">
-        <v>0.1989434429227222</v>
+        <v>0.1987440853352683</v>
       </c>
     </row>
     <row r="46">
@@ -1273,7 +1273,7 @@
         </is>
       </c>
       <c r="D46">
-        <v>0.4587582857763733</v>
+        <v>0.458298572484328</v>
       </c>
     </row>
     <row r="47">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="D51">
-        <v>3.738055624929058</v>
+        <v>3.734309787719214</v>
       </c>
     </row>
     <row r="52">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="D52">
-        <v>1.215411562316626</v>
+        <v>1.21419362060783</v>
       </c>
     </row>
     <row r="53">
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="D56">
-        <v>2.726956862639453</v>
+        <v>2.713530360308236</v>
       </c>
     </row>
     <row r="57">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="D57">
-        <v>2.757242558622307</v>
+        <v>2.754479576256883</v>
       </c>
     </row>
     <row r="58">
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="D58">
-        <v>0.1207864889217274</v>
+        <v>0.1206654509891638</v>
       </c>
     </row>
     <row r="59">
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="D59">
-        <v>1.559679218676141</v>
+        <v>1.549021316311972</v>
       </c>
     </row>
     <row r="60">
